--- a/08_tables/within_between_variance_all_variables.xlsx
+++ b/08_tables/within_between_variance_all_variables.xlsx
@@ -501,19 +501,19 @@
         <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>1348.442960964228</v>
+        <v>1348.442960964223</v>
       </c>
       <c r="G2" t="n">
         <v>2.163732768606204e-28</v>
       </c>
       <c r="H2" t="n">
-        <v>1348.442960964228</v>
+        <v>1348.442960964227</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>1.000000000000003</v>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>100.0000000000003</v>
       </c>
     </row>
     <row r="3">
@@ -537,19 +537,19 @@
         <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>872.3433451891411</v>
+        <v>872.3433451891415</v>
       </c>
       <c r="G3" t="n">
         <v>55.03663535238096</v>
       </c>
       <c r="H3" t="n">
-        <v>820.9072373831776</v>
+        <v>820.9072373831783</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9410368542505346</v>
+        <v>0.9410368542505351</v>
       </c>
       <c r="J3" t="n">
-        <v>94.10368542505346</v>
+        <v>94.10368542505351</v>
       </c>
     </row>
     <row r="4">
@@ -573,19 +573,19 @@
         <v>49.33333333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>263.6537344554319</v>
+        <v>263.6537344554321</v>
       </c>
       <c r="G4" t="n">
         <v>17.18138721936481</v>
       </c>
       <c r="H4" t="n">
-        <v>247.4173592969143</v>
+        <v>247.417359296914</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9384178070071594</v>
+        <v>0.9384178070071575</v>
       </c>
       <c r="J4" t="n">
-        <v>93.84178070071594</v>
+        <v>93.84178070071574</v>
       </c>
     </row>
     <row r="5">
@@ -615,13 +615,13 @@
         <v>2.187417669984873</v>
       </c>
       <c r="H5" t="n">
-        <v>28.70318444709144</v>
+        <v>28.70318444709146</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9335127871318936</v>
+        <v>0.9335127871318945</v>
       </c>
       <c r="J5" t="n">
-        <v>93.35127871318936</v>
+        <v>93.35127871318944</v>
       </c>
     </row>
     <row r="6">
@@ -645,19 +645,19 @@
         <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>23.48778640871892</v>
+        <v>23.4877864087189</v>
       </c>
       <c r="G6" t="n">
         <v>1.83351443312498</v>
       </c>
       <c r="H6" t="n">
-        <v>21.77422151794791</v>
+        <v>21.77422151794794</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9270444280719909</v>
+        <v>0.9270444280719927</v>
       </c>
       <c r="J6" t="n">
-        <v>92.7044428071991</v>
+        <v>92.70444280719927</v>
       </c>
     </row>
     <row r="7">
@@ -681,19 +681,19 @@
         <v>49.33333333333334</v>
       </c>
       <c r="F7" t="n">
-        <v>395.573880280757</v>
+        <v>395.5738802807567</v>
       </c>
       <c r="G7" t="n">
-        <v>92.79769598876443</v>
+        <v>92.79769598876445</v>
       </c>
       <c r="H7" t="n">
         <v>312.5349157813048</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7900797584498866</v>
+        <v>0.7900797584498872</v>
       </c>
       <c r="J7" t="n">
-        <v>79.00797584498866</v>
+        <v>79.00797584498872</v>
       </c>
     </row>
     <row r="8">
@@ -723,13 +723,13 @@
         <v>55.36119098976639</v>
       </c>
       <c r="H8" t="n">
-        <v>112.9496531051156</v>
+        <v>112.9496531051155</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6858356996420448</v>
+        <v>0.6858356996420444</v>
       </c>
       <c r="J8" t="n">
-        <v>68.58356996420449</v>
+        <v>68.58356996420444</v>
       </c>
     </row>
     <row r="9">
@@ -753,19 +753,19 @@
         <v>49.33333333333334</v>
       </c>
       <c r="F9" t="n">
-        <v>29.32443082324543</v>
+        <v>29.32443082324547</v>
       </c>
       <c r="G9" t="n">
         <v>12.06877353095238</v>
       </c>
       <c r="H9" t="n">
-        <v>18.05168274695534</v>
+        <v>18.05168274695536</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6155851022569823</v>
+        <v>0.6155851022569819</v>
       </c>
       <c r="J9" t="n">
-        <v>61.55851022569823</v>
+        <v>61.55851022569819</v>
       </c>
     </row>
     <row r="10">
@@ -792,16 +792,16 @@
         <v>15.69426215456055</v>
       </c>
       <c r="G10" t="n">
-        <v>7.467596369576174</v>
+        <v>7.467596369576175</v>
       </c>
       <c r="H10" t="n">
         <v>8.635988727225</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5502640800934685</v>
+        <v>0.5502640800934686</v>
       </c>
       <c r="J10" t="n">
-        <v>55.02640800934685</v>
+        <v>55.02640800934686</v>
       </c>
     </row>
     <row r="11">
@@ -828,16 +828,16 @@
         <v>777802.4477831916</v>
       </c>
       <c r="G11" t="n">
-        <v>542980.8786611788</v>
+        <v>542980.8786611789</v>
       </c>
       <c r="H11" t="n">
-        <v>284644.3067918816</v>
+        <v>284644.3067918817</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3659596438699106</v>
+        <v>0.3659596438699108</v>
       </c>
       <c r="J11" t="n">
-        <v>36.59596438699106</v>
+        <v>36.59596438699108</v>
       </c>
     </row>
     <row r="12">
@@ -861,7 +861,7 @@
         <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>9538300539555.928</v>
+        <v>9538300539555.934</v>
       </c>
       <c r="G12" t="n">
         <v>8535066003362.101</v>
@@ -870,10 +870,10 @@
         <v>1561603340152.097</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1637192426130872</v>
+        <v>0.1637192426130871</v>
       </c>
       <c r="J12" t="n">
-        <v>16.37192426130872</v>
+        <v>16.37192426130871</v>
       </c>
     </row>
     <row r="13">
@@ -897,7 +897,7 @@
         <v>39.2</v>
       </c>
       <c r="F13" t="n">
-        <v>2840238.137665328</v>
+        <v>2840238.137665327</v>
       </c>
       <c r="G13" t="n">
         <v>2358682.778143684</v>
@@ -906,10 +906,10 @@
         <v>153043.2396819284</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05388394643828341</v>
+        <v>0.05388394643828344</v>
       </c>
       <c r="J13" t="n">
-        <v>5.388394643828341</v>
+        <v>5.388394643828344</v>
       </c>
     </row>
     <row r="14">
@@ -939,13 +939,13 @@
         <v>1101519843.432913</v>
       </c>
       <c r="H14" t="n">
-        <v>46619487.8643631</v>
+        <v>46619487.86436307</v>
       </c>
       <c r="I14" t="n">
-        <v>0.04299318312247748</v>
+        <v>0.04299318312247744</v>
       </c>
       <c r="J14" t="n">
-        <v>4.299318312247748</v>
+        <v>4.299318312247745</v>
       </c>
     </row>
   </sheetData>

--- a/08_tables/within_between_variance_all_variables.xlsx
+++ b/08_tables/within_between_variance_all_variables.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,19 +501,19 @@
         <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>1348.442960964223</v>
+        <v>1348.442960964228</v>
       </c>
       <c r="G2" t="n">
         <v>2.163732768606204e-28</v>
       </c>
       <c r="H2" t="n">
-        <v>1348.442960964227</v>
+        <v>1348.442960964228</v>
       </c>
       <c r="I2" t="n">
-        <v>1.000000000000003</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>100.0000000000003</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -537,19 +537,19 @@
         <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>872.3433451891415</v>
+        <v>872.3433451891411</v>
       </c>
       <c r="G3" t="n">
         <v>55.03663535238096</v>
       </c>
       <c r="H3" t="n">
-        <v>820.9072373831783</v>
+        <v>820.9072373831776</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9410368542505351</v>
+        <v>0.9410368542505346</v>
       </c>
       <c r="J3" t="n">
-        <v>94.10368542505351</v>
+        <v>94.10368542505346</v>
       </c>
     </row>
     <row r="4">
@@ -573,19 +573,19 @@
         <v>49.33333333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>263.6537344554321</v>
+        <v>263.6537344554319</v>
       </c>
       <c r="G4" t="n">
         <v>17.18138721936481</v>
       </c>
       <c r="H4" t="n">
-        <v>247.417359296914</v>
+        <v>247.4173592969143</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9384178070071575</v>
+        <v>0.9384178070071594</v>
       </c>
       <c r="J4" t="n">
-        <v>93.84178070071574</v>
+        <v>93.84178070071594</v>
       </c>
     </row>
     <row r="5">
@@ -615,13 +615,13 @@
         <v>2.187417669984873</v>
       </c>
       <c r="H5" t="n">
-        <v>28.70318444709146</v>
+        <v>28.70318444709144</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9335127871318945</v>
+        <v>0.9335127871318936</v>
       </c>
       <c r="J5" t="n">
-        <v>93.35127871318944</v>
+        <v>93.35127871318936</v>
       </c>
     </row>
     <row r="6">
@@ -645,19 +645,19 @@
         <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>23.4877864087189</v>
+        <v>23.48778640871892</v>
       </c>
       <c r="G6" t="n">
         <v>1.83351443312498</v>
       </c>
       <c r="H6" t="n">
-        <v>21.77422151794794</v>
+        <v>21.77422151794791</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9270444280719927</v>
+        <v>0.9270444280719909</v>
       </c>
       <c r="J6" t="n">
-        <v>92.70444280719927</v>
+        <v>92.7044428071991</v>
       </c>
     </row>
     <row r="7">
@@ -681,19 +681,19 @@
         <v>49.33333333333334</v>
       </c>
       <c r="F7" t="n">
-        <v>395.5738802807567</v>
+        <v>395.573880280757</v>
       </c>
       <c r="G7" t="n">
-        <v>92.79769598876445</v>
+        <v>92.79769598876443</v>
       </c>
       <c r="H7" t="n">
         <v>312.5349157813048</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7900797584498872</v>
+        <v>0.7900797584498866</v>
       </c>
       <c r="J7" t="n">
-        <v>79.00797584498872</v>
+        <v>79.00797584498866</v>
       </c>
     </row>
     <row r="8">
@@ -723,13 +723,13 @@
         <v>55.36119098976639</v>
       </c>
       <c r="H8" t="n">
-        <v>112.9496531051155</v>
+        <v>112.9496531051156</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6858356996420444</v>
+        <v>0.6858356996420448</v>
       </c>
       <c r="J8" t="n">
-        <v>68.58356996420444</v>
+        <v>68.58356996420449</v>
       </c>
     </row>
     <row r="9">
@@ -753,19 +753,19 @@
         <v>49.33333333333334</v>
       </c>
       <c r="F9" t="n">
-        <v>29.32443082324547</v>
+        <v>29.32443082324543</v>
       </c>
       <c r="G9" t="n">
         <v>12.06877353095238</v>
       </c>
       <c r="H9" t="n">
-        <v>18.05168274695536</v>
+        <v>18.05168274695534</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6155851022569819</v>
+        <v>0.6155851022569823</v>
       </c>
       <c r="J9" t="n">
-        <v>61.55851022569819</v>
+        <v>61.55851022569823</v>
       </c>
     </row>
     <row r="10">
@@ -792,16 +792,16 @@
         <v>15.69426215456055</v>
       </c>
       <c r="G10" t="n">
-        <v>7.467596369576175</v>
+        <v>7.467596369576174</v>
       </c>
       <c r="H10" t="n">
         <v>8.635988727225</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5502640800934686</v>
+        <v>0.5502640800934685</v>
       </c>
       <c r="J10" t="n">
-        <v>55.02640800934686</v>
+        <v>55.02640800934685</v>
       </c>
     </row>
     <row r="11">
@@ -828,16 +828,16 @@
         <v>777802.4477831916</v>
       </c>
       <c r="G11" t="n">
-        <v>542980.8786611789</v>
+        <v>542980.8786611788</v>
       </c>
       <c r="H11" t="n">
-        <v>284644.3067918817</v>
+        <v>284644.3067918816</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3659596438699108</v>
+        <v>0.3659596438699106</v>
       </c>
       <c r="J11" t="n">
-        <v>36.59596438699108</v>
+        <v>36.59596438699106</v>
       </c>
     </row>
     <row r="12">
@@ -861,7 +861,7 @@
         <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>9538300539555.934</v>
+        <v>9538300539555.928</v>
       </c>
       <c r="G12" t="n">
         <v>8535066003362.101</v>
@@ -870,10 +870,10 @@
         <v>1561603340152.097</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1637192426130871</v>
+        <v>0.1637192426130872</v>
       </c>
       <c r="J12" t="n">
-        <v>16.37192426130871</v>
+        <v>16.37192426130872</v>
       </c>
     </row>
     <row r="13">
@@ -897,7 +897,7 @@
         <v>39.2</v>
       </c>
       <c r="F13" t="n">
-        <v>2840238.137665327</v>
+        <v>2840238.137665328</v>
       </c>
       <c r="G13" t="n">
         <v>2358682.778143684</v>
@@ -906,10 +906,10 @@
         <v>153043.2396819284</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05388394643828344</v>
+        <v>0.05388394643828341</v>
       </c>
       <c r="J13" t="n">
-        <v>5.388394643828344</v>
+        <v>5.388394643828341</v>
       </c>
     </row>
     <row r="14">
@@ -939,13 +939,13 @@
         <v>1101519843.432913</v>
       </c>
       <c r="H14" t="n">
-        <v>46619487.86436307</v>
+        <v>46619487.8643631</v>
       </c>
       <c r="I14" t="n">
-        <v>0.04299318312247744</v>
+        <v>0.04299318312247748</v>
       </c>
       <c r="J14" t="n">
-        <v>4.299318312247745</v>
+        <v>4.299318312247748</v>
       </c>
     </row>
   </sheetData>

--- a/08_tables/within_between_variance_all_variables.xlsx
+++ b/08_tables/within_between_variance_all_variables.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/08_tables/within_between_variance_all_variables.xlsx
+++ b/08_tables/within_between_variance_all_variables.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,52 +417,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Variable in words</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>NT</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>NT/N</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Overall variance</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Between variance</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Within variance</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Within share</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Within share (%)</t>
         </is>
@@ -488,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Energy commodity price index, PCOM</t>
+          <t>Commodity price index, PCOM</t>
         </is>
       </c>
       <c r="C2" t="n">
